--- a/STUDENTAssignment(1).xlsx
+++ b/STUDENTAssignment(1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joy.nmdrevsup\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joy.nmdrevsup\Desktop\Piety coder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8C951B6-B4A6-441D-9CAD-52B6698B2DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB668A86-1DDE-4470-A02E-B5677E82909E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="109">
   <si>
     <t>STUDENT ID</t>
   </si>
@@ -283,12 +305,6 @@
     <t>Fatima Lawal</t>
   </si>
   <si>
-    <t>Name:</t>
-  </si>
-  <si>
-    <t>Student ID:</t>
-  </si>
-  <si>
     <t>Department</t>
   </si>
   <si>
@@ -298,9 +314,6 @@
     <t>SUBJECTS</t>
   </si>
   <si>
-    <t>SCORE</t>
-  </si>
-  <si>
     <t>GRADE</t>
   </si>
   <si>
@@ -316,9 +329,6 @@
     <t>EXCELLENT</t>
   </si>
   <si>
-    <t>GRADE CLASSIFICATION</t>
-  </si>
-  <si>
     <t>80-100</t>
   </si>
   <si>
@@ -350,13 +360,40 @@
   </si>
   <si>
     <t>NUMBER OF SUBJECT</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>total Average</t>
+  </si>
+  <si>
+    <t>Student ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRADE </t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>POSITION</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>SCORE/100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -425,6 +462,20 @@
       <name val="Segoe Fluent Icons"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe Fluent Icons"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe Fluent Icons"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -435,7 +486,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.499984740745262"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,22 +518,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -490,29 +552,278 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Segoe Fluent Icons"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Segoe Fluent Icons"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Segoe Fluent Icons"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Segoe Fluent Icons"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Segoe Fluent Icons"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Segoe Fluent Icons"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="'Segoe UI'"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="'Segoe UI'"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="'Segoe UI'"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="'Segoe UI'"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -730,7 +1041,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{1710D4EA-3483-4A94-A9E4-EEB91842092D}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -770,8 +1083,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="613231" y="390072"/>
-          <a:ext cx="5546272" cy="1124856"/>
+          <a:off x="619278" y="381001"/>
+          <a:ext cx="5349725" cy="1100665"/>
           <a:chOff x="830944" y="517072"/>
           <a:chExt cx="5168189" cy="1124856"/>
         </a:xfrm>
@@ -917,21 +1230,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BC3A45DC-3D95-4A1B-B81D-B19A07B2F051}" name="Result" displayName="Result" ref="A1:J31" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J31" xr:uid="{BC3A45DC-3D95-4A1B-B81D-B19A07B2F051}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{3F81594C-D38A-45A3-A439-D13BBC5368B9}" name="STUDENT ID" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{76980332-C9F6-408D-8972-E7E8448C59C5}" name="NAME" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{68508035-1E6F-4431-8AEF-8C46EC38B1CF}" name="DEPT" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{150F171E-6F68-4740-AF07-D2B928E32D22}" name="MATHS" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{ACC65F77-96C0-4AEC-AB7D-3E2739D057DC}" name="ENGLISH" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{E16C25E0-D000-4C69-B095-CEA645B02652}" name="PHY" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{67DBF80B-A600-4AFA-853D-06E90705E13D}" name="BIO" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{0270152C-B573-450B-8E2E-D6B44AB6120E}" name="CHE" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{EC2CD4A8-EA99-4969-AD0E-5CC4463043C8}" name="AGRIC" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{628E6B5C-6D2D-4159-98E9-107BFBA5BE14}" name="GEO" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BC3A45DC-3D95-4A1B-B81D-B19A07B2F051}" name="Result" displayName="Result" ref="A1:N31" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:N31" xr:uid="{BC3A45DC-3D95-4A1B-B81D-B19A07B2F051}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{3F81594C-D38A-45A3-A439-D13BBC5368B9}" name="STUDENT ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{76980332-C9F6-408D-8972-E7E8448C59C5}" name="NAME" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{68508035-1E6F-4431-8AEF-8C46EC38B1CF}" name="DEPT" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{150F171E-6F68-4740-AF07-D2B928E32D22}" name="MATHS" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{ACC65F77-96C0-4AEC-AB7D-3E2739D057DC}" name="ENGLISH" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{E16C25E0-D000-4C69-B095-CEA645B02652}" name="PHY" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{67DBF80B-A600-4AFA-853D-06E90705E13D}" name="BIO" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{0270152C-B573-450B-8E2E-D6B44AB6120E}" name="CHE" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{EC2CD4A8-EA99-4969-AD0E-5CC4463043C8}" name="AGRIC" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{628E6B5C-6D2D-4159-98E9-107BFBA5BE14}" name="GEO" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{8025C2C3-5C6A-42C4-9B29-F09CB8D1CBA9}" name="total Average" dataDxfId="9">
+      <calculatedColumnFormula array="1">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{8B075BB5-E23C-4C80-8073-D45FB5764858}" name="Column1" dataDxfId="8">
+      <calculatedColumnFormula>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{DFDFF353-9C1F-47F1-A3E6-C11CCAA721D8}" name="Average" dataDxfId="7">
+      <calculatedColumnFormula>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{5911515E-C6C5-495D-B5E1-E99FFB346AC8}" name="Position" dataDxfId="6">
+      <calculatedColumnFormula>RANK(M2,$M$2:$M$31,0)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3087B259-2833-4CB6-B69F-586C1074D248}" name="Table1" displayName="Table1" ref="O5:P10" headerRowCount="0" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9F3DD44B-919A-417E-A9A9-07D25760F61C}" name="Column1" headerRowDxfId="0" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{EBDA60E8-24A7-456A-BB8A-E78DF36DAFCC}" name="Column2" headerRowDxfId="1" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1136,15 +1471,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.08984375" customWidth="1"/>
     <col min="2" max="2" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6328125" style="8"/>
+    <col min="13" max="14" width="12.6328125" style="8"/>
+    <col min="15" max="15" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14">
+    <row r="1" spans="1:17" ht="14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,8 +1513,24 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="14">
+      <c r="K1" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="Q1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1207,8 +1561,29 @@
       <c r="J2" s="2">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="14">
+      <c r="K2" s="7" cm="1">
+        <f t="array" ref="K2">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>63.571428571428562</v>
+      </c>
+      <c r="L2" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>GOOD</v>
+      </c>
+      <c r="M2" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>63.571428571428569</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" ref="N2:N31" si="0">RANK(M2,$M$2:$M$31,0)</f>
+        <v>24</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -1239,8 +1614,29 @@
       <c r="J3" s="2">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="14">
+      <c r="K3" s="7" cm="1">
+        <f t="array" ref="K3">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>58.857142857142854</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>GOOD</v>
+      </c>
+      <c r="M3" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>58.857142857142854</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="14">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1271,8 +1667,27 @@
       <c r="J4" s="2">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="14">
+      <c r="K4" s="7" cm="1">
+        <f t="array" ref="K4">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>78.428571428571431</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M4" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>78.428571428571431</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1303,8 +1718,29 @@
       <c r="J5" s="2">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="14">
+      <c r="K5" s="7" cm="1">
+        <f t="array" ref="K5">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>77.285714285714278</v>
+      </c>
+      <c r="L5" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M5" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>77.285714285714292</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -1335,8 +1771,29 @@
       <c r="J6" s="2">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="14">
+      <c r="K6" s="7" cm="1">
+        <f t="array" ref="K6">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>62.714285714285722</v>
+      </c>
+      <c r="L6" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>GOOD</v>
+      </c>
+      <c r="M6" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>62.714285714285715</v>
+      </c>
+      <c r="N6" s="7">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1367,8 +1824,29 @@
       <c r="J7" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="14">
+      <c r="K7" s="7" cm="1">
+        <f t="array" ref="K7">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M7" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>65</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1399,8 +1877,26 @@
       <c r="J8" s="2">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="14">
+      <c r="K8" s="7" cm="1">
+        <f t="array" ref="K8">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>70.571428571428569</v>
+      </c>
+      <c r="L8" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M8" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>70.571428571428569</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+    </row>
+    <row r="9" spans="1:17" ht="15">
       <c r="A9" s="2" t="s">
         <v>31</v>
       </c>
@@ -1431,8 +1927,26 @@
       <c r="J9" s="2">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="14">
+      <c r="K9" s="7" cm="1">
+        <f t="array" ref="K9">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>69</v>
+      </c>
+      <c r="L9" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M9" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>69</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+    </row>
+    <row r="10" spans="1:17" ht="15">
       <c r="A10" s="2" t="s">
         <v>34</v>
       </c>
@@ -1463,8 +1977,26 @@
       <c r="J10" s="2">
         <v>69</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="14">
+      <c r="K10" s="7" cm="1">
+        <f t="array" ref="K10">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>71.428571428571431</v>
+      </c>
+      <c r="L10" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M10" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>71.428571428571431</v>
+      </c>
+      <c r="N10" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+    </row>
+    <row r="11" spans="1:17" ht="14">
       <c r="A11" s="2" t="s">
         <v>37</v>
       </c>
@@ -1495,8 +2027,24 @@
       <c r="J11" s="2">
         <v>74</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="14">
+      <c r="K11" s="7" cm="1">
+        <f t="array" ref="K11">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>68.857142857142861</v>
+      </c>
+      <c r="L11" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M11" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>68.857142857142861</v>
+      </c>
+      <c r="N11" s="7">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="14">
       <c r="A12" s="2" t="s">
         <v>39</v>
       </c>
@@ -1527,8 +2075,24 @@
       <c r="J12" s="2">
         <v>66</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="14">
+      <c r="K12" s="7" cm="1">
+        <f t="array" ref="K12">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>65.857142857142861</v>
+      </c>
+      <c r="L12" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M12" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>65.857142857142861</v>
+      </c>
+      <c r="N12" s="7">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="14">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
@@ -1559,8 +2123,24 @@
       <c r="J13" s="2">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="14">
+      <c r="K13" s="7" cm="1">
+        <f t="array" ref="K13">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>71</v>
+      </c>
+      <c r="L13" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M13" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>71</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="14">
       <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
@@ -1591,8 +2171,24 @@
       <c r="J14" s="2">
         <v>72</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="14">
+      <c r="K14" s="7" cm="1">
+        <f t="array" ref="K14">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>67.857142857142861</v>
+      </c>
+      <c r="L14" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M14" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>67.857142857142861</v>
+      </c>
+      <c r="N14" s="7">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="14">
       <c r="A15" s="2" t="s">
         <v>46</v>
       </c>
@@ -1623,8 +2219,24 @@
       <c r="J15" s="2">
         <v>82</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="14">
+      <c r="K15" s="7" cm="1">
+        <f t="array" ref="K15">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>69.714285714285708</v>
+      </c>
+      <c r="L15" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M15" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>69.714285714285708</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="14">
       <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
@@ -1655,8 +2267,24 @@
       <c r="J16" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="14">
+      <c r="K16" s="7" cm="1">
+        <f t="array" ref="K16">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>62.571428571428577</v>
+      </c>
+      <c r="L16" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>GOOD</v>
+      </c>
+      <c r="M16" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>62.571428571428569</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="14">
       <c r="A17" s="2" t="s">
         <v>51</v>
       </c>
@@ -1687,8 +2315,24 @@
       <c r="J17" s="2">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="14">
+      <c r="K17" s="7" cm="1">
+        <f t="array" ref="K17">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>67.142857142857139</v>
+      </c>
+      <c r="L17" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M17" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>67.142857142857139</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="14">
       <c r="A18" s="2" t="s">
         <v>53</v>
       </c>
@@ -1719,8 +2363,24 @@
       <c r="J18" s="2">
         <v>70</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="14">
+      <c r="K18" s="7" cm="1">
+        <f t="array" ref="K18">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>66</v>
+      </c>
+      <c r="L18" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M18" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>66</v>
+      </c>
+      <c r="N18" s="7">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="14">
       <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
@@ -1751,8 +2411,24 @@
       <c r="J19" s="2">
         <v>68</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="14">
+      <c r="K19" s="7" cm="1">
+        <f t="array" ref="K19">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>71.571428571428569</v>
+      </c>
+      <c r="L19" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M19" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>71.571428571428569</v>
+      </c>
+      <c r="N19" s="7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="14">
       <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
@@ -1783,8 +2459,24 @@
       <c r="J20" s="2">
         <v>67</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="14">
+      <c r="K20" s="7" cm="1">
+        <f t="array" ref="K20">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>71.142857142857139</v>
+      </c>
+      <c r="L20" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M20" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>71.142857142857139</v>
+      </c>
+      <c r="N20" s="7">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="14">
       <c r="A21" s="2" t="s">
         <v>59</v>
       </c>
@@ -1815,8 +2507,24 @@
       <c r="J21" s="2">
         <v>79</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="14">
+      <c r="K21" s="7" cm="1">
+        <f t="array" ref="K21">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>60.142857142857146</v>
+      </c>
+      <c r="L21" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>GOOD</v>
+      </c>
+      <c r="M21" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>60.142857142857146</v>
+      </c>
+      <c r="N21" s="7">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="14">
       <c r="A22" s="2" t="s">
         <v>61</v>
       </c>
@@ -1847,8 +2555,24 @@
       <c r="J22" s="2">
         <v>70</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="14">
+      <c r="K22" s="7" cm="1">
+        <f t="array" ref="K22">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>73.285714285714292</v>
+      </c>
+      <c r="L22" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M22" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>73.285714285714292</v>
+      </c>
+      <c r="N22" s="7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="14">
       <c r="A23" s="2" t="s">
         <v>63</v>
       </c>
@@ -1879,8 +2603,24 @@
       <c r="J23" s="2">
         <v>81</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="14">
+      <c r="K23" s="7" cm="1">
+        <f t="array" ref="K23">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>71.428571428571431</v>
+      </c>
+      <c r="L23" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M23" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>71.428571428571431</v>
+      </c>
+      <c r="N23" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="14">
       <c r="A24" s="2" t="s">
         <v>65</v>
       </c>
@@ -1911,8 +2651,24 @@
       <c r="J24" s="2">
         <v>73</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="14">
+      <c r="K24" s="7" cm="1">
+        <f t="array" ref="K24">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>78.285714285714292</v>
+      </c>
+      <c r="L24" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M24" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>78.285714285714292</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="14">
       <c r="A25" s="2" t="s">
         <v>67</v>
       </c>
@@ -1943,8 +2699,24 @@
       <c r="J25" s="2">
         <v>69</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="14">
+      <c r="K25" s="7" cm="1">
+        <f t="array" ref="K25">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>69.714285714285708</v>
+      </c>
+      <c r="L25" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M25" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>69.714285714285708</v>
+      </c>
+      <c r="N25" s="7">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="14">
       <c r="A26" s="2" t="s">
         <v>69</v>
       </c>
@@ -1975,8 +2747,24 @@
       <c r="J26" s="2">
         <v>75</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="14">
+      <c r="K26" s="7" cm="1">
+        <f t="array" ref="K26">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>76.857142857142847</v>
+      </c>
+      <c r="L26" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M26" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>76.857142857142861</v>
+      </c>
+      <c r="N26" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="14">
       <c r="A27" s="2" t="s">
         <v>71</v>
       </c>
@@ -2007,8 +2795,24 @@
       <c r="J27" s="2">
         <v>64</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="14">
+      <c r="K27" s="7" cm="1">
+        <f t="array" ref="K27">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>63.428571428571416</v>
+      </c>
+      <c r="L27" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>GOOD</v>
+      </c>
+      <c r="M27" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>63.428571428571431</v>
+      </c>
+      <c r="N27" s="7">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="14">
       <c r="A28" s="2" t="s">
         <v>73</v>
       </c>
@@ -2039,8 +2843,24 @@
       <c r="J28" s="2">
         <v>74</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="14">
+      <c r="K28" s="7" cm="1">
+        <f t="array" ref="K28">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>60.714285714285708</v>
+      </c>
+      <c r="L28" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>GOOD</v>
+      </c>
+      <c r="M28" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>60.714285714285715</v>
+      </c>
+      <c r="N28" s="7">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="14">
       <c r="A29" s="2" t="s">
         <v>75</v>
       </c>
@@ -2071,8 +2891,24 @@
       <c r="J29" s="2">
         <v>72</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="14">
+      <c r="K29" s="7" cm="1">
+        <f t="array" ref="K29">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>67.285714285714292</v>
+      </c>
+      <c r="L29" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M29" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>67.285714285714292</v>
+      </c>
+      <c r="N29" s="7">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="14">
       <c r="A30" s="2" t="s">
         <v>77</v>
       </c>
@@ -2103,8 +2939,24 @@
       <c r="J30" s="2">
         <v>71</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="14">
+      <c r="K30" s="7" cm="1">
+        <f t="array" ref="K30">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>76.999999999999986</v>
+      </c>
+      <c r="L30" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M30" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>77</v>
+      </c>
+      <c r="N30" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="14">
       <c r="A31" s="2" t="s">
         <v>79</v>
       </c>
@@ -2135,11 +2987,31 @@
       <c r="J31" s="2">
         <v>69</v>
       </c>
+      <c r="K31" s="7" cm="1">
+        <f t="array" ref="K31">SUM(Result[[#This Row],[MATHS]:[GEO]]/7)</f>
+        <v>72</v>
+      </c>
+      <c r="L31" s="2" t="str">
+        <f>IF(Result[[#This Row],[total Average]]&gt;=80,"ËXCELLENT",IF(Result[[#This Row],[total Average]]&gt;=65,"V. GOOD", IF(Result[[#This Row],[total Average]]&gt;=55,"GOOD",IF(Result[[#This Row],[total Average]]&gt;=45,"PASS",IF(Result[[#This Row],[total Average]]&lt;=44,"FAIL")))))</f>
+        <v>V. GOOD</v>
+      </c>
+      <c r="M31" s="7">
+        <f>AVERAGE(Result[[#This Row],[MATHS]:[GEO]])</f>
+        <v>72</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="O3:P3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2149,562 +3021,568 @@
   <dimension ref="A2:M37"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.90625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="8.7265625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.90625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="2.6328125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.453125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.90625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="7.7265625" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:9" ht="12.5" customHeight="1">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" ht="12.5" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" ht="12.5" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" ht="12.5" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" ht="29.5" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" ht="13.5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" ht="13.5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="10" t="s">
+    <row r="2" spans="1:12">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" ht="12.5" customHeight="1">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" ht="12.5" customHeight="1">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" ht="12.5" customHeight="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:12" ht="12.5" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:12" ht="29.5" customHeight="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5">
+      <c r="A10" s="11"/>
+      <c r="B10" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="11"/>
+      <c r="L10" s="27"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5">
+      <c r="A11" s="11"/>
+      <c r="B11" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="14" t="str">
+        <f>_xlfn.XLOOKUP(C10,'Result DB'!A2:A31,'Result DB'!B2:B31," No Name",0)</f>
+        <v>Adeola Musa</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5">
+      <c r="A12" s="11"/>
+      <c r="B12" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="10" t="str">
-        <f>_xlfn.XLOOKUP(C10,'Result DB'!A2:A31,'Result DB'!B2:B31," No Name",0)</f>
-        <v>Chinedu Nnamdi</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" ht="13.5">
-      <c r="A12" s="4"/>
-      <c r="B12" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="10" t="str">
+      <c r="C12" s="14" t="str">
         <f>VLOOKUP(C10,'Result DB'!A:C,3,FALSE)</f>
         <v>Computer Science</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" ht="13.5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" ht="13.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" ht="13.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="11" t="s">
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5">
+      <c r="A13" s="11"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:12" ht="13.5">
+      <c r="A14" s="11"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:12" ht="13.5">
+      <c r="A15" s="11"/>
+      <c r="B15" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="11" t="s">
+      <c r="F15" s="15"/>
+      <c r="G15" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:12" ht="13.5">
+      <c r="A16" s="11"/>
+      <c r="B16" s="16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="26">
+        <f>VLOOKUP($C$10,Result[],4,FALSE)</f>
+        <v>78</v>
+      </c>
+      <c r="E16" s="19" t="str">
+        <f>IF(D16&gt;80,"EXCELLENT",IF(D16&gt;65,"V.GOOD",IF(D16&gt;55,"GOOD",IF(D16&gt;44,"PASS","FAIL"))))</f>
+        <v>V.GOOD</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:13" ht="13.5">
+      <c r="A17" s="11"/>
+      <c r="B17" s="16">
+        <v>2</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="26">
+        <f>VLOOKUP($C$10,Result[],5,FALSE)</f>
+        <v>65</v>
+      </c>
+      <c r="E17" s="19" t="str">
+        <f t="shared" ref="E17:E22" si="0">IF(D17&gt;80,"EXCELLENT",IF(D17&gt;65,"V.GOOD",IF(D17&gt;55,"GOOD",IF(D17&gt;44,"PASS","FAIL"))))</f>
+        <v>GOOD</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:13" ht="13.5">
+      <c r="A18" s="11"/>
+      <c r="B18" s="16">
+        <v>3</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="26">
+        <f>VLOOKUP($C$10,Result[],6,FALSE)</f>
+        <v>44</v>
+      </c>
+      <c r="E18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="13.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="11">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="8">
-        <f>VLOOKUP($C$10,Result[],4,FALSE)</f>
-        <v>82</v>
-      </c>
-      <c r="E16" s="8" t="str">
-        <f>IF(D16&gt;80,"EXCELLENT",IF(D16&gt;65,"V.GOOD",IF(D16&gt;55,"GOOD",IF(D16&gt;44,"PASS","FAIL"))))</f>
-        <v>EXCELLENT</v>
-      </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:13" ht="13.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="11">
-        <v>2</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:13" ht="13.5">
+      <c r="A19" s="11"/>
+      <c r="B19" s="16">
         <v>4</v>
       </c>
-      <c r="D17" s="8">
-        <f>VLOOKUP($C$10,Result[],5,FALSE)</f>
-        <v>79</v>
-      </c>
-      <c r="E17" s="8" t="str">
-        <f t="shared" ref="E17:E22" si="0">IF(D17&gt;80,"EXCELLENT",IF(D17&gt;65,"V.GOOD",IF(D17&gt;55,"GOOD",IF(D17&gt;44,"PASS","FAIL"))))</f>
-        <v>V.GOOD</v>
-      </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:13" ht="13.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="11">
-        <v>3</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="8">
-        <f>VLOOKUP($C$10,Result[],6,FALSE)</f>
-        <v>84</v>
-      </c>
-      <c r="E18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>EXCELLENT</v>
-      </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:13" ht="13.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="11">
-        <v>4</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="26">
         <f>VLOOKUP($C$10,Result[],7,FALSE)</f>
-        <v>80</v>
-      </c>
-      <c r="E19" s="8" t="str">
+        <v>74</v>
+      </c>
+      <c r="E19" s="19" t="str">
         <f t="shared" si="0"/>
         <v>V.GOOD</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="4"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:13" ht="13.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="11">
+      <c r="A20" s="11"/>
+      <c r="B20" s="16">
         <v>5</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="26">
         <f>VLOOKUP($C$10,Result[],8,FALSE)</f>
-        <v>78</v>
-      </c>
-      <c r="E20" s="8" t="str">
+        <v>69</v>
+      </c>
+      <c r="E20" s="19" t="str">
         <f t="shared" si="0"/>
         <v>V.GOOD</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="8" t="s">
+      <c r="F20" s="15"/>
+      <c r="G20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:13" ht="13.5">
+      <c r="A21" s="11"/>
+      <c r="B21" s="16">
+        <v>6</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="26">
+        <f>VLOOKUP($C$10,Result[],9,FALSE)</f>
+        <v>55</v>
+      </c>
+      <c r="E21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:13" ht="13.5">
+      <c r="A22" s="11"/>
+      <c r="B22" s="16">
+        <v>7</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="26">
+        <f>VLOOKUP($C$10,Result[],10,FALSE)</f>
+        <v>60</v>
+      </c>
+      <c r="E22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>GOOD</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:13" ht="13.5">
+      <c r="A23" s="11"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="11"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="1:13" ht="13.5">
+      <c r="A24" s="11"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:13" ht="13.5">
+      <c r="A25" s="11"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="11"/>
+    </row>
+    <row r="26" spans="1:13" ht="13.5">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="26">
+        <f>SUM(D16:D22)</f>
+        <v>445</v>
+      </c>
+      <c r="I26" s="14"/>
+    </row>
+    <row r="27" spans="1:13" ht="13.5">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="28">
+        <f>AVERAGE(D16:D22)</f>
+        <v>63.571428571428569</v>
+      </c>
+      <c r="I27" s="29"/>
+    </row>
+    <row r="28" spans="1:13" ht="13.5">
+      <c r="A28" s="11"/>
+      <c r="B28" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="31">
+        <f>_xlfn.XLOOKUP(C10,'Result DB'!A:A,'Result DB'!N:N,"NON",0)</f>
+        <v>24</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" spans="1:13" ht="13.5">
+      <c r="A29" s="11"/>
+      <c r="B29" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:13" ht="13.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="11">
-        <v>6</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="8">
-        <f>VLOOKUP($C$10,Result[],9,FALSE)</f>
-        <v>72</v>
-      </c>
-      <c r="E21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>V.GOOD</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="1:13" ht="13.5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="11">
-        <v>7</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="8">
-        <f>VLOOKUP($C$10,Result[],10,FALSE)</f>
-        <v>73</v>
-      </c>
-      <c r="E22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>V.GOOD</v>
-      </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="1:13" ht="13.5">
-      <c r="A23" s="4"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="4"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-    </row>
-    <row r="24" spans="1:13" ht="13.5">
-      <c r="A24" s="4"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="1:13" ht="13.5">
-      <c r="A25" s="4"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="4"/>
-    </row>
-    <row r="26" spans="1:13" ht="13.5">
-      <c r="A26" s="4"/>
-      <c r="B26" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="15">
-        <f>SUM(D16:D22)</f>
-        <v>548</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="4"/>
-    </row>
-    <row r="27" spans="1:13" ht="13.5">
-      <c r="A27" s="4"/>
-      <c r="B27" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" s="16">
-        <f>AVERAGE(D16:D22)</f>
-        <v>78.285714285714292</v>
-      </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="4"/>
-    </row>
-    <row r="28" spans="1:13" ht="13.5">
-      <c r="A28" s="4"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="4"/>
-    </row>
-    <row r="29" spans="1:13" ht="13.5">
-      <c r="A29" s="4"/>
-      <c r="B29" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="9">
+      <c r="C29" s="30"/>
+      <c r="D29" s="26">
         <f>COUNTA(Result[NAME])</f>
         <v>30</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="4"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:13" ht="13.5">
-      <c r="A30" s="4"/>
-      <c r="B30" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="9">
+      <c r="A30" s="11"/>
+      <c r="B30" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="32"/>
+      <c r="D30" s="26">
         <f>COUNTA(C16:C22)</f>
         <v>7</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="4"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:13" ht="14.5">
-      <c r="A32" s="19"/>
-      <c r="B32" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="19"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="4"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="19"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="4"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
+  <mergeCells count="7">
+    <mergeCell ref="B33:H34"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G15:H15"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:H34"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
